--- a/xlsx/carteira_mensal/Jun_2026.xlsx
+++ b/xlsx/carteira_mensal/Jun_2026.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="111">
   <si>
     <t>Acompanhamento de Carteira</t>
   </si>
@@ -75,24 +75,24 @@
     <t>Data de Criação do Projeto</t>
   </si>
   <si>
+    <t>/  /     até   /  /</t>
+  </si>
+  <si>
+    <t>Data de Criação do Orçamento</t>
+  </si>
+  <si>
+    <t>/  /     00:00 até   /  /     00:00</t>
+  </si>
+  <si>
+    <t>Data de Criação do Contrato</t>
+  </si>
+  <si>
+    <t>Data de Assinatura do Contrato</t>
+  </si>
+  <si>
     <t>01/06/2026 até 30/06/2026</t>
   </si>
   <si>
-    <t>Data de Criação do Orçamento</t>
-  </si>
-  <si>
-    <t>/  /     00:00 até   /  /     00:00</t>
-  </si>
-  <si>
-    <t>Data de Criação do Contrato</t>
-  </si>
-  <si>
-    <t>/  /     até   /  /</t>
-  </si>
-  <si>
-    <t>Data de Assinatura do Contrato</t>
-  </si>
-  <si>
     <t>Data de Criação do Cliente</t>
   </si>
   <si>
@@ -153,6 +153,66 @@
     <t>Contrato</t>
   </si>
   <si>
+    <t>EDUARDO CASULO ALVAREZ</t>
+  </si>
+  <si>
+    <t>Google</t>
+  </si>
+  <si>
+    <t>02/05/26</t>
+  </si>
+  <si>
+    <t>ROSANGELA PACHECO</t>
+  </si>
+  <si>
+    <t>Orçamento 1</t>
+  </si>
+  <si>
+    <t>18/06/26</t>
+  </si>
+  <si>
+    <t>Patricia Souza Fernandez</t>
+  </si>
+  <si>
+    <t>16/05/26</t>
+  </si>
+  <si>
+    <t>Orçamento 2</t>
+  </si>
+  <si>
+    <t>27/06/26</t>
+  </si>
+  <si>
+    <t>Nicole Costa Brito</t>
+  </si>
+  <si>
+    <t>28/05/26</t>
+  </si>
+  <si>
+    <t>BIANCA RODRIGUES</t>
+  </si>
+  <si>
+    <t>19/06/26</t>
+  </si>
+  <si>
+    <t>13/06/26</t>
+  </si>
+  <si>
+    <t>Ana Bia Fonseca Ferreira</t>
+  </si>
+  <si>
+    <t>Porta</t>
+  </si>
+  <si>
+    <t>29/05/26</t>
+  </si>
+  <si>
+    <t>Rubens Felipe de Siqueira Costa</t>
+  </si>
+  <si>
+    <t>03/06/26</t>
+  </si>
+  <si>
     <t>Andre Luiz Soy Ribeiro</t>
   </si>
   <si>
@@ -165,9 +225,6 @@
     <t>ERIC SERPA</t>
   </si>
   <si>
-    <t>Orçamento 1</t>
-  </si>
-  <si>
     <t>Elaine Massumi Higashi</t>
   </si>
   <si>
@@ -180,12 +237,6 @@
     <t>Maria Clara Salles Viana Pereira Coutinho</t>
   </si>
   <si>
-    <t>Google</t>
-  </si>
-  <si>
-    <t>ROSANGELA PACHECO</t>
-  </si>
-  <si>
     <t>12/06/26</t>
   </si>
   <si>
@@ -198,9 +249,6 @@
     <t>17/06/26</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
-  </si>
-  <si>
     <t>22/06/26</t>
   </si>
   <si>
@@ -213,30 +261,12 @@
     <t>Fábrica</t>
   </si>
   <si>
-    <t>Orçamento 2</t>
-  </si>
-  <si>
     <t>24/06/26</t>
   </si>
   <si>
     <t>Camila Ferreira Stoqui</t>
   </si>
   <si>
-    <t>Porta</t>
-  </si>
-  <si>
-    <t>18/06/26</t>
-  </si>
-  <si>
-    <t>27/06/26</t>
-  </si>
-  <si>
-    <t>Nicole Costa Brito</t>
-  </si>
-  <si>
-    <t>19/06/26</t>
-  </si>
-  <si>
     <t>BRUNO ATAYDE LEAO</t>
   </si>
   <si>
@@ -273,7 +303,7 @@
     <t>Quantidade de Projetos</t>
   </si>
   <si>
-    <t>11</t>
+    <t>15</t>
   </si>
   <si>
     <t>Quantidade de Orçamentos</t>
@@ -288,34 +318,34 @@
     <t>Valor Total Bruto</t>
   </si>
   <si>
-    <t>833.462,27</t>
-  </si>
-  <si>
-    <t>579.655,50</t>
+    <t>1.055.465,81</t>
+  </si>
+  <si>
+    <t>737.685,50</t>
   </si>
   <si>
     <t>Valor Total Líquido</t>
   </si>
   <si>
-    <t>545.702,53</t>
+    <t>693.165,03</t>
   </si>
   <si>
     <t>Total Líquido sem o Per</t>
   </si>
   <si>
-    <t>540.266,35</t>
+    <t>686.255,38</t>
   </si>
   <si>
     <t>Total Diferença Financeira</t>
   </si>
   <si>
-    <t>33.952,97</t>
+    <t>44.520,47</t>
   </si>
   <si>
     <t>Total Adicional dos Ambientes</t>
   </si>
   <si>
-    <t>28.630,53</t>
+    <t>35.139,21</t>
   </si>
 </sst>
 </file>
@@ -384,7 +414,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:O52"/>
+  <dimension ref="A2:O56"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="53.22265625" customWidth="true" bestFit="true"/>
@@ -512,15 +542,15 @@
         <v>23</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -528,7 +558,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -536,7 +566,7 @@
         <v>27</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -642,7 +672,7 @@
         <v>47</v>
       </c>
       <c r="C31" t="n">
-        <v>829.0</v>
+        <v>767.0</v>
       </c>
       <c r="D31" t="s">
         <v>48</v>
@@ -657,139 +687,139 @@
         <v>50</v>
       </c>
       <c r="H31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I31" t="n">
-        <v>16800.0</v>
+        <v>86500.0</v>
       </c>
       <c r="J31" t="n">
-        <v>0.0</v>
+        <v>3173.92</v>
       </c>
       <c r="K31" t="n">
-        <v>16800.0</v>
+        <v>83326.08</v>
       </c>
       <c r="L31" t="n">
-        <v>15200.0</v>
+        <v>83326.08</v>
       </c>
       <c r="M31" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="N31" t="n">
-        <v>82901.0</v>
+        <v>76701.0</v>
       </c>
       <c r="O31" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B32" t="s">
         <v>47</v>
       </c>
       <c r="C32" t="n">
-        <v>832.0</v>
+        <v>792.0</v>
       </c>
       <c r="D32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G32" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="I32" t="n">
-        <v>250000.0</v>
+        <v>900.0</v>
       </c>
       <c r="J32" t="n">
-        <v>9022.94</v>
+        <v>44.03</v>
       </c>
       <c r="K32" t="n">
-        <v>240977.06</v>
+        <v>855.97</v>
       </c>
       <c r="L32" t="n">
-        <v>240977.06</v>
+        <v>855.97</v>
       </c>
       <c r="M32" t="n">
-        <v>1.9</v>
+        <v>4.55</v>
       </c>
       <c r="N32" t="n">
-        <v>83201.0</v>
+        <v>79202.0</v>
       </c>
       <c r="O32" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>56</v>
+      </c>
+      <c r="B33" t="s">
+        <v>47</v>
+      </c>
+      <c r="C33" t="n">
+        <v>819.0</v>
+      </c>
+      <c r="D33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" t="s">
+        <v>58</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G33" t="s">
         <v>54</v>
       </c>
-      <c r="B33" t="s">
-        <v>55</v>
-      </c>
-      <c r="C33" t="n">
-        <v>830.0</v>
-      </c>
-      <c r="D33" t="s">
-        <v>52</v>
-      </c>
-      <c r="E33" t="s">
-        <v>56</v>
-      </c>
-      <c r="F33" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G33" t="s">
-        <v>50</v>
-      </c>
       <c r="H33" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I33" t="n">
-        <v>12384.22</v>
+        <v>70000.0</v>
       </c>
       <c r="J33" t="n">
-        <v>454.41</v>
+        <v>7334.01</v>
       </c>
       <c r="K33" t="n">
-        <v>11929.81</v>
+        <v>62665.99</v>
       </c>
       <c r="L33" t="n">
-        <v>11929.81</v>
+        <v>61192.52</v>
       </c>
       <c r="M33" t="n">
-        <v>2.3</v>
+        <v>1.95</v>
       </c>
       <c r="N33" t="n">
-        <v>83001.0</v>
+        <v>81902.0</v>
       </c>
       <c r="O33" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C34" t="n">
-        <v>842.0</v>
+        <v>822.0</v>
       </c>
       <c r="D34" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E34" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F34" t="n">
         <v>1.0</v>
@@ -798,92 +828,92 @@
         <v>50</v>
       </c>
       <c r="H34" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I34" t="n">
-        <v>70000.0</v>
+        <v>630.0</v>
       </c>
       <c r="J34" t="n">
-        <v>2568.49</v>
+        <v>15.54</v>
       </c>
       <c r="K34" t="n">
-        <v>67431.51</v>
+        <v>614.46</v>
       </c>
       <c r="L34" t="n">
-        <v>64869.55</v>
+        <v>614.46</v>
       </c>
       <c r="M34" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="N34" t="n">
-        <v>84201.0</v>
+        <v>82201.0</v>
       </c>
       <c r="O34" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C35" t="n">
-        <v>841.0</v>
+        <v>829.0</v>
       </c>
       <c r="D35" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E35" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="F35" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="G35" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I35" t="n">
-        <v>65195.33</v>
+        <v>16800.0</v>
       </c>
       <c r="J35" t="n">
-        <v>12517.46</v>
+        <v>0.0</v>
       </c>
       <c r="K35" t="n">
-        <v>52677.87</v>
+        <v>16800.0</v>
       </c>
       <c r="L35" t="n">
-        <v>51403.65</v>
+        <v>15200.0</v>
       </c>
       <c r="M35" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
       <c r="N35" t="n">
-        <v>84102.0</v>
+        <v>82901.0</v>
       </c>
       <c r="O35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B36" t="s">
+        <v>67</v>
+      </c>
+      <c r="C36" t="n">
+        <v>832.0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" t="s">
         <v>69</v>
-      </c>
-      <c r="C36" t="n">
-        <v>844.0</v>
-      </c>
-      <c r="D36" t="s">
-        <v>70</v>
-      </c>
-      <c r="E36" t="s">
-        <v>61</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
@@ -892,45 +922,45 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I36" t="n">
-        <v>9500.0</v>
+        <v>250000.0</v>
       </c>
       <c r="J36" t="n">
-        <v>679.88</v>
+        <v>9022.94</v>
       </c>
       <c r="K36" t="n">
-        <v>8820.12</v>
+        <v>240977.06</v>
       </c>
       <c r="L36" t="n">
-        <v>8820.12</v>
+        <v>240977.06</v>
       </c>
       <c r="M36" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="N36" t="n">
-        <v>84401.0</v>
+        <v>83201.0</v>
       </c>
       <c r="O36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C37" t="n">
-        <v>846.0</v>
+        <v>830.0</v>
       </c>
       <c r="D37" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E37" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="F37" t="n">
         <v>1.0</v>
@@ -939,45 +969,45 @@
         <v>50</v>
       </c>
       <c r="H37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I37" t="n">
-        <v>300.0</v>
+        <v>12384.22</v>
       </c>
       <c r="J37" t="n">
-        <v>0.0</v>
+        <v>454.41</v>
       </c>
       <c r="K37" t="n">
-        <v>300.0</v>
+        <v>11929.81</v>
       </c>
       <c r="L37" t="n">
-        <v>300.0</v>
+        <v>11929.81</v>
       </c>
       <c r="M37" t="n">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="N37" t="n">
-        <v>84601.0</v>
+        <v>83001.0</v>
       </c>
       <c r="O37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B38" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="C38" t="n">
-        <v>852.0</v>
+        <v>842.0</v>
       </c>
       <c r="D38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E38" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F38" t="n">
         <v>1.0</v>
@@ -986,92 +1016,92 @@
         <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="I38" t="n">
-        <v>135000.0</v>
+        <v>70000.0</v>
       </c>
       <c r="J38" t="n">
-        <v>6135.6</v>
+        <v>2568.49</v>
       </c>
       <c r="K38" t="n">
-        <v>128864.4</v>
+        <v>67431.51</v>
       </c>
       <c r="L38" t="n">
-        <v>128864.4</v>
+        <v>64869.55</v>
       </c>
       <c r="M38" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="N38" t="n">
-        <v>85201.0</v>
+        <v>84201.0</v>
       </c>
       <c r="O38" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C39" t="n">
+        <v>841.0</v>
+      </c>
+      <c r="D39" t="s">
         <v>77</v>
       </c>
-      <c r="B39" t="s">
-        <v>78</v>
-      </c>
-      <c r="C39" t="n">
-        <v>857.0</v>
-      </c>
-      <c r="D39" t="s">
-        <v>67</v>
-      </c>
       <c r="E39" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F39" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G39" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="H39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="I39" t="n">
-        <v>14000.0</v>
+        <v>65195.33</v>
       </c>
       <c r="J39" t="n">
-        <v>2068.47</v>
+        <v>12517.46</v>
       </c>
       <c r="K39" t="n">
-        <v>11931.53</v>
+        <v>52677.87</v>
       </c>
       <c r="L39" t="n">
-        <v>11931.53</v>
+        <v>51403.65</v>
       </c>
       <c r="M39" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="N39" t="n">
-        <v>85701.0</v>
+        <v>84102.0</v>
       </c>
       <c r="O39" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B40" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="C40" t="n">
-        <v>856.0</v>
+        <v>844.0</v>
       </c>
       <c r="D40" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
@@ -1080,45 +1110,45 @@
         <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="I40" t="n">
-        <v>1375.95</v>
+        <v>9500.0</v>
       </c>
       <c r="J40" t="n">
-        <v>79.9</v>
+        <v>679.88</v>
       </c>
       <c r="K40" t="n">
-        <v>1296.05</v>
+        <v>8820.12</v>
       </c>
       <c r="L40" t="n">
-        <v>1296.05</v>
+        <v>8820.12</v>
       </c>
       <c r="M40" t="n">
-        <v>2.73</v>
+        <v>1.93</v>
       </c>
       <c r="N40" t="n">
-        <v>85601.0</v>
+        <v>84401.0</v>
       </c>
       <c r="O40" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C41" t="n">
-        <v>858.0</v>
+        <v>846.0</v>
       </c>
       <c r="D41" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="E41" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
@@ -1127,100 +1157,288 @@
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="I41" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="K41" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>300.0</v>
+      </c>
+      <c r="M41" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="N41" t="n">
+        <v>84601.0</v>
+      </c>
+      <c r="O41" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>84</v>
+      </c>
+      <c r="B42" t="s">
+        <v>47</v>
+      </c>
+      <c r="C42" t="n">
+        <v>852.0</v>
+      </c>
+      <c r="D42" t="s">
+        <v>85</v>
+      </c>
+      <c r="E42" t="s">
+        <v>58</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G42" t="s">
+        <v>50</v>
+      </c>
+      <c r="H42" t="s">
+        <v>86</v>
+      </c>
+      <c r="I42" t="n">
+        <v>135000.0</v>
+      </c>
+      <c r="J42" t="n">
+        <v>6135.6</v>
+      </c>
+      <c r="K42" t="n">
+        <v>128864.4</v>
+      </c>
+      <c r="L42" t="n">
+        <v>128864.4</v>
+      </c>
+      <c r="M42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="N42" t="n">
+        <v>85201.0</v>
+      </c>
+      <c r="O42" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>87</v>
+      </c>
+      <c r="B43" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" t="n">
+        <v>857.0</v>
+      </c>
+      <c r="D43" t="s">
+        <v>82</v>
+      </c>
+      <c r="E43" t="s">
+        <v>49</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G43" t="s">
+        <v>50</v>
+      </c>
+      <c r="H43" t="s">
+        <v>89</v>
+      </c>
+      <c r="I43" t="n">
+        <v>14000.0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2068.47</v>
+      </c>
+      <c r="K43" t="n">
+        <v>11931.53</v>
+      </c>
+      <c r="L43" t="n">
+        <v>11931.53</v>
+      </c>
+      <c r="M43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N43" t="n">
+        <v>85701.0</v>
+      </c>
+      <c r="O43" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>90</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" t="n">
+        <v>856.0</v>
+      </c>
+      <c r="D44" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G44" t="s">
+        <v>50</v>
+      </c>
+      <c r="H44" t="s">
+        <v>82</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1375.95</v>
+      </c>
+      <c r="J44" t="n">
+        <v>79.9</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1296.05</v>
+      </c>
+      <c r="L44" t="n">
+        <v>1296.05</v>
+      </c>
+      <c r="M44" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="N44" t="n">
+        <v>85601.0</v>
+      </c>
+      <c r="O44" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>47</v>
+      </c>
+      <c r="C45" t="n">
+        <v>858.0</v>
+      </c>
+      <c r="D45" t="s">
+        <v>93</v>
+      </c>
+      <c r="E45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G45" t="s">
+        <v>50</v>
+      </c>
+      <c r="H45" t="s">
+        <v>93</v>
+      </c>
+      <c r="I45" t="n">
         <v>5100.0</v>
       </c>
-      <c r="J41" t="n">
+      <c r="J45" t="n">
         <v>425.82</v>
       </c>
-      <c r="K41" t="n">
+      <c r="K45" t="n">
         <v>4674.18</v>
       </c>
-      <c r="L41" t="n">
+      <c r="L45" t="n">
         <v>4674.18</v>
       </c>
-      <c r="M41" t="n">
+      <c r="M45" t="n">
         <v>2.1</v>
       </c>
-      <c r="N41" t="n">
+      <c r="N45" t="n">
         <v>85801.0</v>
       </c>
-      <c r="O41" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>91</v>
+      <c r="O45" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>99</v>
+        <v>17</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/xlsx/carteira_mensal/Jun_2026.xlsx
+++ b/xlsx/carteira_mensal/Jun_2026.xlsx
@@ -728,7 +728,7 @@
         <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="G32" t="s">
         <v>54</v>

--- a/xlsx/carteira_mensal/Jun_2026.xlsx
+++ b/xlsx/carteira_mensal/Jun_2026.xlsx
@@ -174,6 +174,9 @@
     <t>Patricia Souza Fernandez</t>
   </si>
   <si>
+    <t>Já é Cliente</t>
+  </si>
+  <si>
     <t>16/05/26</t>
   </si>
   <si>
@@ -277,9 +280,6 @@
   </si>
   <si>
     <t>Thiago de Souza Silva</t>
-  </si>
-  <si>
-    <t>Já é Cliente</t>
   </si>
   <si>
     <t>26/06/26</t>
@@ -716,25 +716,25 @@
         <v>52</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C32" t="n">
         <v>792.0</v>
       </c>
       <c r="D32" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E32" t="s">
         <v>49</v>
       </c>
       <c r="F32" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G32" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I32" t="n">
         <v>900.0</v>
@@ -755,12 +755,12 @@
         <v>79202.0</v>
       </c>
       <c r="O32" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B33" t="s">
         <v>47</v>
@@ -769,19 +769,19 @@
         <v>819.0</v>
       </c>
       <c r="D33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E33" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F33" t="n">
         <v>3.0</v>
       </c>
       <c r="G33" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H33" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I33" t="n">
         <v>70000.0</v>
@@ -802,24 +802,24 @@
         <v>81902.0</v>
       </c>
       <c r="O33" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C34" t="n">
         <v>822.0</v>
       </c>
       <c r="D34" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="E34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F34" t="n">
         <v>1.0</v>
@@ -828,7 +828,7 @@
         <v>50</v>
       </c>
       <c r="H34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I34" t="n">
         <v>630.0</v>
@@ -849,24 +849,24 @@
         <v>82201.0</v>
       </c>
       <c r="O34" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" t="n">
         <v>829.0</v>
       </c>
       <c r="D35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F35" t="n">
         <v>1.0</v>
@@ -875,7 +875,7 @@
         <v>50</v>
       </c>
       <c r="H35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I35" t="n">
         <v>16800.0</v>
@@ -896,24 +896,24 @@
         <v>82901.0</v>
       </c>
       <c r="O35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C36" t="n">
         <v>832.0</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F36" t="n">
         <v>1.0</v>
@@ -922,7 +922,7 @@
         <v>50</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="n">
         <v>250000.0</v>
@@ -943,12 +943,12 @@
         <v>83201.0</v>
       </c>
       <c r="O36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
         <v>47</v>
@@ -957,7 +957,7 @@
         <v>830.0</v>
       </c>
       <c r="D37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E37" t="s">
         <v>49</v>
@@ -969,7 +969,7 @@
         <v>50</v>
       </c>
       <c r="H37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I37" t="n">
         <v>12384.22</v>
@@ -990,24 +990,24 @@
         <v>83001.0</v>
       </c>
       <c r="O37" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B38" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C38" t="n">
         <v>842.0</v>
       </c>
       <c r="D38" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F38" t="n">
         <v>1.0</v>
@@ -1016,7 +1016,7 @@
         <v>50</v>
       </c>
       <c r="H38" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I38" t="n">
         <v>70000.0</v>
@@ -1037,21 +1037,21 @@
         <v>84201.0</v>
       </c>
       <c r="O38" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B39" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C39" t="n">
         <v>841.0</v>
       </c>
       <c r="D39" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E39" t="s">
         <v>49</v>
@@ -1060,10 +1060,10 @@
         <v>2.0</v>
       </c>
       <c r="G39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I39" t="n">
         <v>65195.33</v>
@@ -1084,15 +1084,15 @@
         <v>84102.0</v>
       </c>
       <c r="O39" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B40" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C40" t="n">
         <v>844.0</v>
@@ -1101,7 +1101,7 @@
         <v>51</v>
       </c>
       <c r="E40" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F40" t="n">
         <v>1.0</v>
@@ -1110,7 +1110,7 @@
         <v>50</v>
       </c>
       <c r="H40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="I40" t="n">
         <v>9500.0</v>
@@ -1131,12 +1131,12 @@
         <v>84401.0</v>
       </c>
       <c r="O40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B41" t="s">
         <v>47</v>
@@ -1145,10 +1145,10 @@
         <v>846.0</v>
       </c>
       <c r="D41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E41" t="s">
         <v>59</v>
-      </c>
-      <c r="E41" t="s">
-        <v>58</v>
       </c>
       <c r="F41" t="n">
         <v>1.0</v>
@@ -1157,7 +1157,7 @@
         <v>50</v>
       </c>
       <c r="H41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I41" t="n">
         <v>300.0</v>
@@ -1178,12 +1178,12 @@
         <v>84601.0</v>
       </c>
       <c r="O41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B42" t="s">
         <v>47</v>
@@ -1192,10 +1192,10 @@
         <v>852.0</v>
       </c>
       <c r="D42" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E42" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F42" t="n">
         <v>1.0</v>
@@ -1204,7 +1204,7 @@
         <v>50</v>
       </c>
       <c r="H42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I42" t="n">
         <v>135000.0</v>
@@ -1225,21 +1225,21 @@
         <v>85201.0</v>
       </c>
       <c r="O42" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B43" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="C43" t="n">
         <v>857.0</v>
       </c>
       <c r="D43" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E43" t="s">
         <v>49</v>
@@ -1286,7 +1286,7 @@
         <v>856.0</v>
       </c>
       <c r="D44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E44" t="s">
         <v>91</v>
@@ -1298,7 +1298,7 @@
         <v>50</v>
       </c>
       <c r="H44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I44" t="n">
         <v>1375.95</v>
@@ -1319,7 +1319,7 @@
         <v>85601.0</v>
       </c>
       <c r="O44" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45">

--- a/xlsx/carteira_mensal/Jun_2026.xlsx
+++ b/xlsx/carteira_mensal/Jun_2026.xlsx
@@ -192,7 +192,7 @@
     <t>28/05/26</t>
   </si>
   <si>
-    <t>BIANCA RODRIGUES</t>
+    <t>bianca rodrigues</t>
   </si>
   <si>
     <t>19/06/26</t>
